--- a/variables.xlsx
+++ b/variables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c502c410f1ad430/문서/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c502c410f1ad430/바탕 화면/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2119B2CA-09D0-4B9B-A485-84BCEF41F12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{2119B2CA-09D0-4B9B-A485-84BCEF41F12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{752AB56B-B48C-44DE-B2C6-6C923A9FFE40}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{1EFFD572-6CE3-4C25-9F73-616CA1E95787}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{1EFFD572-6CE3-4C25-9F73-616CA1E95787}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,118 +41,123 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
+    <t>Aceh</t>
+  </si>
+  <si>
+    <t>Sumatera Utara</t>
+  </si>
+  <si>
+    <t>Sumatera Barat</t>
+  </si>
+  <si>
+    <t>Riau</t>
+  </si>
+  <si>
+    <t>Jambi</t>
+  </si>
+  <si>
+    <t>Sumatera Selatan</t>
+  </si>
+  <si>
+    <t>Bengkulu</t>
+  </si>
+  <si>
+    <t>Lampung</t>
+  </si>
+  <si>
+    <t>Kep. Bangka Belitung</t>
+  </si>
+  <si>
+    <t>Kepulauan Riau</t>
+  </si>
+  <si>
+    <t>DKI Jakarta</t>
+  </si>
+  <si>
+    <t>Jawa Barat</t>
+  </si>
+  <si>
+    <t>Jawa Tengah</t>
+  </si>
+  <si>
+    <t>DI Yogyakarta</t>
+  </si>
+  <si>
+    <t>Jawa Timur</t>
+  </si>
+  <si>
+    <t>Banten</t>
+  </si>
+  <si>
+    <t>Bali</t>
+  </si>
+  <si>
+    <t>Nusa Tenggara Barat</t>
+  </si>
+  <si>
+    <t>Nusa Tenggara Timur</t>
+  </si>
+  <si>
+    <t>Kalimantan Barat</t>
+  </si>
+  <si>
+    <t>Kalimantan Tengah</t>
+  </si>
+  <si>
+    <t>Kalimantan Selatan</t>
+  </si>
+  <si>
+    <t>Kalimantan Timur</t>
+  </si>
+  <si>
+    <t>Sulawesi Utara</t>
+  </si>
+  <si>
+    <t>Sulawesi Tengah</t>
+  </si>
+  <si>
+    <t>Sulawesi Selatan</t>
+  </si>
+  <si>
+    <t>Sulawesi Tenggara</t>
+  </si>
+  <si>
+    <t>Gorontalo</t>
+  </si>
+  <si>
+    <t>Sulawesi Barat</t>
+  </si>
+  <si>
+    <t>Maluku</t>
+  </si>
+  <si>
+    <t>Maluku Utara</t>
+  </si>
+  <si>
+    <t>Papua Barat</t>
+  </si>
+  <si>
+    <t>Papua</t>
+  </si>
+  <si>
     <t>Province</t>
-  </si>
-  <si>
-    <t>1인당 GDP(2007)</t>
-  </si>
-  <si>
-    <t>1인당 GDP(2025)</t>
-  </si>
-  <si>
-    <t>빈곤율(2007)</t>
-  </si>
-  <si>
-    <t>빈곤율(2025)</t>
-  </si>
-  <si>
-    <t>Aceh</t>
-  </si>
-  <si>
-    <t>Sumatera Utara</t>
-  </si>
-  <si>
-    <t>Sumatera Barat</t>
-  </si>
-  <si>
-    <t>Riau</t>
-  </si>
-  <si>
-    <t>Jambi</t>
-  </si>
-  <si>
-    <t>Sumatera Selatan</t>
-  </si>
-  <si>
-    <t>Bengkulu</t>
-  </si>
-  <si>
-    <t>Lampung</t>
-  </si>
-  <si>
-    <t>Kep. Bangka Belitung</t>
-  </si>
-  <si>
-    <t>Kepulauan Riau</t>
-  </si>
-  <si>
-    <t>DKI Jakarta</t>
-  </si>
-  <si>
-    <t>Jawa Barat</t>
-  </si>
-  <si>
-    <t>Jawa Tengah</t>
-  </si>
-  <si>
-    <t>DI Yogyakarta</t>
-  </si>
-  <si>
-    <t>Jawa Timur</t>
-  </si>
-  <si>
-    <t>Banten</t>
-  </si>
-  <si>
-    <t>Bali</t>
-  </si>
-  <si>
-    <t>Nusa Tenggara Barat</t>
-  </si>
-  <si>
-    <t>Nusa Tenggara Timur</t>
-  </si>
-  <si>
-    <t>Kalimantan Barat</t>
-  </si>
-  <si>
-    <t>Kalimantan Tengah</t>
-  </si>
-  <si>
-    <t>Kalimantan Selatan</t>
-  </si>
-  <si>
-    <t>Kalimantan Timur</t>
-  </si>
-  <si>
-    <t>Sulawesi Utara</t>
-  </si>
-  <si>
-    <t>Sulawesi Tengah</t>
-  </si>
-  <si>
-    <t>Sulawesi Selatan</t>
-  </si>
-  <si>
-    <t>Sulawesi Tenggara</t>
-  </si>
-  <si>
-    <t>Gorontalo</t>
-  </si>
-  <si>
-    <t>Sulawesi Barat</t>
-  </si>
-  <si>
-    <t>Maluku</t>
-  </si>
-  <si>
-    <t>Maluku Utara</t>
-  </si>
-  <si>
-    <t>Papua Barat</t>
-  </si>
-  <si>
-    <t>Papua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GDP_2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GDP_2007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poverty_2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Poverty_2007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -572,24 +577,24 @@
   <sheetData>
     <row r="1" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A1" s="2" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B2" s="5">
         <v>16832</v>
@@ -606,7 +611,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A3" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B3" s="5">
         <v>14167</v>
@@ -623,7 +628,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5">
         <v>12729</v>
@@ -640,7 +645,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B5" s="5">
         <v>41412</v>
@@ -657,7 +662,7 @@
     </row>
     <row r="6" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B6" s="5">
         <v>11697</v>
@@ -674,7 +679,7 @@
     </row>
     <row r="7" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A7" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5">
         <v>15655</v>
@@ -691,7 +696,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A8" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B8" s="5">
         <v>7930</v>
@@ -708,7 +713,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A9" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9" s="5">
         <v>8357</v>
@@ -725,7 +730,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B10" s="5">
         <v>16170</v>
@@ -742,7 +747,7 @@
     </row>
     <row r="11" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B11" s="5">
         <v>37207</v>
@@ -759,7 +764,7 @@
     </row>
     <row r="12" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B12" s="5">
         <v>62490</v>
@@ -776,7 +781,7 @@
     </row>
     <row r="13" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A13" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5">
         <v>13058</v>
@@ -793,7 +798,7 @@
     </row>
     <row r="14" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A14" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B14" s="5">
         <v>9649</v>
@@ -810,7 +815,7 @@
     </row>
     <row r="15" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A15" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5">
         <v>9584</v>
@@ -827,7 +832,7 @@
     </row>
     <row r="16" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A16" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B16" s="5">
         <v>14498</v>
@@ -844,7 +849,7 @@
     </row>
     <row r="17" spans="1:5" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A17" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B17" s="5">
         <v>11408</v>
@@ -861,7 +866,7 @@
     </row>
     <row r="18" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B18" s="5">
         <v>12166</v>
@@ -878,7 +883,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A19" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B19" s="5">
         <v>7809</v>
@@ -895,7 +900,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A20" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5">
         <v>4302</v>
@@ -912,7 +917,7 @@
     </row>
     <row r="21" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A21" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5">
         <v>10166</v>
@@ -929,7 +934,7 @@
     </row>
     <row r="22" spans="1:5" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A22" s="4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B22" s="5">
         <v>13765</v>
@@ -946,7 +951,7 @@
     </row>
     <row r="23" spans="1:5" ht="47.25" x14ac:dyDescent="0.6">
       <c r="A23" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B23" s="5">
         <v>11611</v>
@@ -963,7 +968,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A24" s="4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B24" s="5">
         <v>70119</v>
@@ -980,7 +985,7 @@
     </row>
     <row r="25" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A25" s="4" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5">
         <v>11012</v>
@@ -997,7 +1002,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A26" s="4" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B26" s="5">
         <v>9074</v>
@@ -1014,7 +1019,7 @@
     </row>
     <row r="27" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A27" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B27" s="5">
         <v>8996</v>
@@ -1031,7 +1036,7 @@
     </row>
     <row r="28" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A28" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B28" s="5">
         <v>8837</v>
@@ -1048,7 +1053,7 @@
     </row>
     <row r="29" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A29" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B29" s="5">
         <v>4958</v>
@@ -1065,7 +1070,7 @@
     </row>
     <row r="30" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A30" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B30" s="5">
         <v>6091</v>
@@ -1082,7 +1087,7 @@
     </row>
     <row r="31" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A31" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B31" s="5">
         <v>4377</v>
@@ -1099,7 +1104,7 @@
     </row>
     <row r="32" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A32" s="4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B32" s="5">
         <v>3346</v>
@@ -1116,7 +1121,7 @@
     </row>
     <row r="33" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A33" s="4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B33" s="5">
         <v>14483</v>
@@ -1133,7 +1138,7 @@
     </row>
     <row r="34" spans="1:5" ht="31.5" x14ac:dyDescent="0.6">
       <c r="A34" s="4" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B34" s="5">
         <v>27476</v>
